--- a/Decks/Breya.xlsx
+++ b/Decks/Breya.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE9971E-33DD-4418-A523-0ACF3D628A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8983C068-4637-4A69-A311-FC0AB7679547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{67D8724E-4F47-4FB1-93E9-E678307D7B49}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{67D8724E-4F47-4FB1-93E9-E678307D7B49}"/>
   </bookViews>
   <sheets>
     <sheet name="Breya" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="116">
   <si>
     <t>Função</t>
   </si>
@@ -378,9 +378,6 @@
   </si>
   <si>
     <t>Phyrexian Altar</t>
-  </si>
-  <si>
-    <t>Ravenous Robots</t>
   </si>
   <si>
     <t>Spirit Water Revival</t>
@@ -1661,10 +1658,10 @@
         <v>0</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D57" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -1721,7 +1718,7 @@
         <v>1</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D61" t="s">
         <v>69</v>
@@ -1913,13 +1910,13 @@
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D74" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -1994,7 +1991,7 @@
         <v>84</v>
       </c>
       <c r="D79" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">

--- a/Decks/Breya.xlsx
+++ b/Decks/Breya.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8983C068-4637-4A69-A311-FC0AB7679547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D657AC-657B-42D8-8FD9-46244A789F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{67D8724E-4F47-4FB1-93E9-E678307D7B49}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{67D8724E-4F47-4FB1-93E9-E678307D7B49}"/>
   </bookViews>
   <sheets>
     <sheet name="Breya" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="115">
   <si>
     <t>Função</t>
   </si>
@@ -89,12 +89,6 @@
     <t>Power Depot</t>
   </si>
   <si>
-    <t>Fundição dos Cônsules</t>
-  </si>
-  <si>
-    <t>Reflecting Pool</t>
-  </si>
-  <si>
     <t>Goldmire Bridge</t>
   </si>
   <si>
@@ -122,9 +116,6 @@
     <t>Command Tower</t>
   </si>
   <si>
-    <t>Castle Embereth</t>
-  </si>
-  <si>
     <t>Spire of Industry</t>
   </si>
   <si>
@@ -260,9 +251,6 @@
     <t>Worldwalker Helm</t>
   </si>
   <si>
-    <t>Pia and Kiran Nalaar</t>
-  </si>
-  <si>
     <t>Grim Hireling</t>
   </si>
   <si>
@@ -284,33 +272,18 @@
     <t>Pitiless Plunderer</t>
   </si>
   <si>
-    <t>Sharding Sphinx</t>
-  </si>
-  <si>
     <t>Biotransference</t>
   </si>
   <si>
-    <t>Saheeli, the Gifted</t>
-  </si>
-  <si>
     <t>Hangarback Walker</t>
   </si>
   <si>
     <t>Cayth, Famed Mechanist</t>
   </si>
   <si>
-    <t>Brudiclad, Telchor Engineer</t>
-  </si>
-  <si>
     <t>Weapons Manufacturing</t>
   </si>
   <si>
-    <t>Saheeli, Filigree Master</t>
-  </si>
-  <si>
-    <t>Daretti, Ingenious Iconoclast</t>
-  </si>
-  <si>
     <t>Retrofitter Foundry</t>
   </si>
   <si>
@@ -332,15 +305,9 @@
     <t>Blink</t>
   </si>
   <si>
-    <t>Eldrazi Displacer</t>
-  </si>
-  <si>
     <t>Thassa, Deep-Dwelling</t>
   </si>
   <si>
-    <t>Soulherder</t>
-  </si>
-  <si>
     <t>Airbender Ascension</t>
   </si>
   <si>
@@ -350,21 +317,12 @@
     <t>Utilidade</t>
   </si>
   <si>
-    <t>Prosperous Partnership</t>
-  </si>
-  <si>
     <t>Lotho, Corrupt Shirriff</t>
   </si>
   <si>
-    <t>Mayhem Devil</t>
-  </si>
-  <si>
     <t>Time Sieve</t>
   </si>
   <si>
-    <t>Tezzeret, Master of the Bridge</t>
-  </si>
-  <si>
     <t>Ashnod's Altar</t>
   </si>
   <si>
@@ -384,6 +342,45 @@
   </si>
   <si>
     <t>Monologue Tax</t>
+  </si>
+  <si>
+    <t>Blasting Station</t>
+  </si>
+  <si>
+    <t>Forensic Gadgeteer</t>
+  </si>
+  <si>
+    <t>Scavenger's Talent</t>
+  </si>
+  <si>
+    <t>Genesis Chamber</t>
+  </si>
+  <si>
+    <t>Elegy Acolyte</t>
+  </si>
+  <si>
+    <t>The Mind Stone</t>
+  </si>
+  <si>
+    <t>The Soul Stone</t>
+  </si>
+  <si>
+    <t>Elesh Norn</t>
+  </si>
+  <si>
+    <t>Scientist Supreme of A.I.M.</t>
+  </si>
+  <si>
+    <t>Endless Sands</t>
+  </si>
+  <si>
+    <t>Teleportation Circle</t>
+  </si>
+  <si>
+    <t>Kingpin, Wilson Fisk</t>
+  </si>
+  <si>
+    <t>Northampton Farm</t>
   </si>
 </sst>
 </file>
@@ -799,7 +796,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.85546875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" style="7" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="41.140625" customWidth="1"/>
     <col min="6" max="6" width="41.140625" style="7" customWidth="1"/>
   </cols>
@@ -844,7 +841,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="5" t="b">
-        <f t="shared" ref="B3:B66" si="0">C3&lt;&gt;D3</f>
+        <f t="shared" ref="B3:B69" si="0">C3&lt;&gt;D3</f>
         <v>0</v>
       </c>
       <c r="C3" s="6" t="s">
@@ -965,13 +962,13 @@
       </c>
       <c r="B11" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -983,10 +980,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -998,10 +995,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1013,10 +1010,10 @@
         <v>0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1028,10 +1025,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1043,10 +1040,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1058,10 +1055,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1073,10 +1070,10 @@
         <v>0</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1088,10 +1085,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1103,10 +1100,10 @@
         <v>0</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1118,10 +1115,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1133,10 +1130,10 @@
         <v>0</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D22" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1148,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1163,10 +1160,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D24" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1178,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D25" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1193,10 +1190,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D26" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1208,10 +1205,10 @@
         <v>0</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1223,10 +1220,10 @@
         <v>0</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D28" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1238,10 +1235,10 @@
         <v>0</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D29" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1253,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D30" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1268,10 +1265,10 @@
         <v>0</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D31" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1283,10 +1280,10 @@
         <v>0</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D32" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1298,10 +1295,10 @@
         <v>0</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D33" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1313,10 +1310,10 @@
         <v>0</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D34" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1328,10 +1325,10 @@
         <v>0</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D35" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1343,10 +1340,10 @@
         <v>0</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D36" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1358,970 +1355,979 @@
         <v>0</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D37" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B38" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D38" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B39" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D39" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>46</v>
-      </c>
       <c r="D40" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B41" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D41" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B42" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D42" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B43" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D43" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B44" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B45" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D45" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D46" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B47" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C47&lt;&gt;D47</f>
         <v>0</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D47" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B48" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C48" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D49" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="5" t="b">
+        <f>C50&lt;&gt;D50</f>
+        <v>0</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D50" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="5" t="b">
+        <f>C51&lt;&gt;D51</f>
+        <v>0</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D51" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>53</v>
+      </c>
+      <c r="B52" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C52" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D52" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C49" s="6" t="s">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C53" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D53" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C54" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B50" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C50" s="6" t="s">
+      <c r="D54" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>53</v>
+      </c>
+      <c r="B55" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C55" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D55" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>56</v>
-      </c>
-      <c r="B51" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C51" s="6" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>53</v>
+      </c>
+      <c r="B56" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C56" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D56" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>56</v>
-      </c>
-      <c r="B52" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C52" s="6" t="s">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>53</v>
+      </c>
+      <c r="B57" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C57" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D57" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>56</v>
-      </c>
-      <c r="B53" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C53" s="6" t="s">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>53</v>
+      </c>
+      <c r="B58" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C58" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D58" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>56</v>
-      </c>
-      <c r="B54" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C54" s="6" t="s">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>53</v>
+      </c>
+      <c r="B59" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D59" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>53</v>
+      </c>
+      <c r="B60" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C60" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D60" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>56</v>
-      </c>
-      <c r="B55" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C55" s="6" t="s">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>53</v>
+      </c>
+      <c r="B61" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D61" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>53</v>
+      </c>
+      <c r="B62" s="5" t="b">
+        <f>C62&lt;&gt;D62</f>
+        <v>0</v>
+      </c>
+      <c r="C62" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D62" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>56</v>
-      </c>
-      <c r="B56" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D56" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>56</v>
-      </c>
-      <c r="B57" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D57" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>56</v>
-      </c>
-      <c r="B58" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C58" s="6" t="s">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>53</v>
+      </c>
+      <c r="B63" s="5" t="b">
+        <f>C63&lt;&gt;D63</f>
+        <v>0</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D63" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>64</v>
       </c>
-      <c r="D58" t="s">
+      <c r="B64" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D64" t="s">
+        <v>66</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>56</v>
-      </c>
-      <c r="B59" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D59" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>56</v>
-      </c>
-      <c r="B60" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D60" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="B65" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C65" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B61" s="5" t="b">
+      <c r="D65" t="s">
+        <v>67</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" s="5" t="b">
+        <f>C66&lt;&gt;D66</f>
+        <v>0</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D66" t="s">
+        <v>104</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>64</v>
+      </c>
+      <c r="B67" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D67" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>64</v>
+      </c>
+      <c r="B68" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D68" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>64</v>
+      </c>
+      <c r="B69" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="C61" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D61" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>67</v>
-      </c>
-      <c r="B62" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D62" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>67</v>
-      </c>
-      <c r="B63" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C63" s="6" t="s">
+      <c r="C69" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D69" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>64</v>
+      </c>
+      <c r="B70" s="5" t="b">
+        <f t="shared" ref="B70:B101" si="1">C70&lt;&gt;D70</f>
+        <v>0</v>
+      </c>
+      <c r="C70" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D70" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>67</v>
-      </c>
-      <c r="B64" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D64" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>67</v>
-      </c>
-      <c r="B65" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D65" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>67</v>
-      </c>
-      <c r="B66" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D66" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>67</v>
-      </c>
-      <c r="B67" s="5" t="b">
-        <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
-        <v>0</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D67" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>67</v>
-      </c>
-      <c r="B68" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D68" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>67</v>
-      </c>
-      <c r="B69" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D69" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>67</v>
-      </c>
-      <c r="B70" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D70" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="D71" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D72" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D73" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D74" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B75" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C75&lt;&gt;D75</f>
         <v>0</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D75" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="D76" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B77" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C77&lt;&gt;D77</f>
         <v>0</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="D77" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D78" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B79" s="5" t="b">
-        <f>C79&lt;&gt;D79</f>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D79" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D80" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B81" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C81&lt;&gt;D81</f>
         <v>0</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D81" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="6" t="s">
-        <v>67</v>
+      <c r="A82" t="s">
+        <v>64</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D82" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D83" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D84" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D85" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D86" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D87" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D88" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="D89" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="D90" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D91" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D92" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B93" s="5" t="b">
         <f>C93&lt;&gt;D93</f>
         <v>0</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="D93" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B94" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C94&lt;&gt;D94</f>
         <v>0</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D94" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B95" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C95&lt;&gt;D95</f>
         <v>0</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D95" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D96" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="D97" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B98" s="5" t="b">
-        <f>C98&lt;&gt;D98</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D98" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B99" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C99&lt;&gt;D99</f>
         <v>0</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D99" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D100" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="D101" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Breya.xlsx
+++ b/Decks/Breya.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D657AC-657B-42D8-8FD9-46244A789F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E8DAF6-2C29-45B3-9AA9-9CD8A3F19A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{67D8724E-4F47-4FB1-93E9-E678307D7B49}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{67D8724E-4F47-4FB1-93E9-E678307D7B49}"/>
   </bookViews>
   <sheets>
     <sheet name="Breya" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="117">
   <si>
     <t>Função</t>
   </si>
@@ -381,6 +381,12 @@
   </si>
   <si>
     <t>Northampton Farm</t>
+  </si>
+  <si>
+    <t>Castle Doom</t>
+  </si>
+  <si>
+    <t>Gleaming Splendor</t>
   </si>
 </sst>
 </file>
@@ -1067,13 +1073,13 @@
       </c>
       <c r="B18" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2006,13 +2012,13 @@
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>79</v>
       </c>
       <c r="D80" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
